--- a/artfynd/A 31722-2023 artfynd.xlsx
+++ b/artfynd/A 31722-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31722-2023 artfynd.xlsx
+++ b/artfynd/A 31722-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,140 +809,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>608220</v>
-      </c>
-      <c r="B3" t="n">
-        <v>104887</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1885</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Klockgentiana</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Gentiana pneumonanthe</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Lillån, norr ån. Hanavrå, 700 m VNV, Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>427564</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6253739</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Osby</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Visseltofta</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Osb-0021</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1992-07-12</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1992-07-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>4D1f1728</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>beteshävdad mad</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Skåne Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Åke Widgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31722-2023 artfynd.xlsx
+++ b/artfynd/A 31722-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72848912</v>
+        <v>608220</v>
       </c>
       <c r="B2" t="n">
-        <v>103415</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>106401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,8 +703,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>427563.6667794226</v>
+        <v>427564</v>
       </c>
       <c r="R2" t="n">
-        <v>6253738.642045098</v>
+        <v>6253739</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,31 +757,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-07-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-07-12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>biotopen bra med lagom betestryck.</t>
+          <t>4D1f1728</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -795,12 +788,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson, Sofia Lund, Kerstin Svensson, Leif Runeson, Ulf Ryde, Ole Tryggeson, Olof Rydén, Göran Nilsson, Johnny Nilsson</t>
+          <t>Åke Widgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
